--- a/docs/Iteration #2 Feature Log.xlsx
+++ b/docs/Iteration #2 Feature Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BC7FFD-5721-42C2-910B-77CD7BA74FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8119094E-AB2D-4F87-B4AE-C12B59E582DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Iteration #1</t>
   </si>
@@ -59,27 +59,12 @@
     <t>Iteration Comments &amp; Summary</t>
   </si>
   <si>
-    <t>Oct 22 2024</t>
-  </si>
-  <si>
     <t>BUILDING USER INTERFACE</t>
   </si>
   <si>
-    <t>Oct 28 2024</t>
-  </si>
-  <si>
-    <t>Nov 04 2024</t>
-  </si>
-  <si>
-    <t>Nov 07 2024</t>
-  </si>
-  <si>
     <t>Dec 1 2024</t>
   </si>
   <si>
-    <t>UserInterface_Form; AccountRegistration; AccountLogin; AccountRestore;</t>
-  </si>
-  <si>
     <t>Implemented</t>
   </si>
   <si>
@@ -89,16 +74,34 @@
     <t>UserInterface_Form</t>
   </si>
   <si>
-    <t>Not Implemented</t>
-  </si>
-  <si>
-    <t>AccountRegistration</t>
-  </si>
-  <si>
-    <t>AccountLogin</t>
-  </si>
-  <si>
-    <t>AccountRestore</t>
+    <t>UsernameValidation_Tests</t>
+  </si>
+  <si>
+    <t>PasswordValidation_Tests</t>
+  </si>
+  <si>
+    <t>EmailValidation_Tests</t>
+  </si>
+  <si>
+    <t>SendingValidInformation_Tests</t>
+  </si>
+  <si>
+    <t>Nov 20 2024</t>
+  </si>
+  <si>
+    <t>Nov 26 2024</t>
+  </si>
+  <si>
+    <t>Nov 27 2024</t>
+  </si>
+  <si>
+    <t>Dec 01 2024</t>
+  </si>
+  <si>
+    <t>UsernameValidation_Tests, PasswordValidation_Tests, EmailValidation_Tests, SendingValidInformation_Tests</t>
+  </si>
+  <si>
+    <t>To successfully bring and work on some critical components it was not the best iteration, yet I did find a replacement of my initial ideas and successfully managed to bring them in a very comprehensive and granular way. Making the tests allowed me to spot critical bugs within the app that I was even surprised to meet, overall over than 45 test methods that checks this features I think this iteration played a very big role because critical components of the application has been tested and yes there was bugs that I had to fix right away.</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.90625" customWidth="1"/>
-    <col min="2" max="2" width="71.7265625" customWidth="1"/>
+    <col min="2" max="2" width="98.81640625" customWidth="1"/>
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
     <col min="4" max="4" width="59.6328125" customWidth="1"/>
     <col min="5" max="5" width="88.08984375" customWidth="1"/>
@@ -503,7 +506,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -523,19 +526,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
@@ -543,19 +546,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
@@ -563,19 +566,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
@@ -583,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -594,7 +597,9 @@
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>

--- a/docs/Iteration #2 Feature Log.xlsx
+++ b/docs/Iteration #2 Feature Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marve\Desktop\RenCloud\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8119094E-AB2D-4F87-B4AE-C12B59E582DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A4EAA2-593F-4697-98E8-0716CD05ADAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
-    <t>Iteration #1</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>To successfully bring and work on some critical components it was not the best iteration, yet I did find a replacement of my initial ideas and successfully managed to bring them in a very comprehensive and granular way. Making the tests allowed me to spot critical bugs within the app that I was even surprised to meet, overall over than 45 test methods that checks this features I think this iteration played a very big role because critical components of the application has been tested and yes there was bugs that I had to fix right away.</t>
+  </si>
+  <si>
+    <t>Iteration #2</t>
   </si>
 </sst>
 </file>
@@ -503,90 +503,90 @@
   <sheetData>
     <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -595,10 +595,10 @@
     </row>
     <row r="6" spans="1:6" ht="64" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
